--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDefaults.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDefaults.verified.xlsx
@@ -106,10 +106,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" sqref="B2:B11">
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="B2:B11">
       <formula1>ISNUMBER(B2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showErrorMessage="1" sqref="C2:C11">
+    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="C2:C11">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDefaults.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDefaults.verified.xlsx
@@ -105,13 +105,16 @@
       <formula>LEN(TRIM(D2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="B2:B11">
       <formula1>ISNUMBER(B2)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: TRUE, FALSE." sqref="C2:C11">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
+    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="D2:D11">
+      <formula1>LEN(TRIM(D2))&gt;0</formula1>
+    </dataValidation>
   </dataValidations>
 </worksheet>
 </file>
--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDefaults.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDefaults.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" r:id="DeterministicId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="1" r:id="DeterministicId3"/>
   </sheets>
 </workbook>
 </file>
@@ -117,4 +117,15 @@
     </dataValidation>
   </dataValidations>
 </worksheet>
+</file>
+
+<file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+  <sheet name="Employees">
+    <column index="1" property="Name"/>
+    <column index="2" property="Age"/>
+    <column index="3" property="IsActive"/>
+    <column index="4" property="HireDate"/>
+  </sheet>
+</columnMetadata>
 </file>